--- a/data/trans_orig/IQ09_D-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_D-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio en días que llevan sufriendo esa dolencia, enfermedad o impedimento que le haya limitado de forma continuada (más de 10 días en los últimos 12 meses)</t>
+          <t>Tiempo medio en días que llevan sufriendo esa dolencia, enfermedad o impedimento que le haya limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 97,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,17 +716,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 16,5</t>
+          <t>1,35; 16,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 9,09</t>
+          <t>1,22; 8,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 2,9</t>
+          <t>0,11; 2,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 14,4</t>
+          <t>2,7; 14,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,94</t>
+          <t>0,0; 1,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -756,22 +756,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,78; 12,83</t>
+          <t>3,61; 13,17</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,14</t>
+          <t>0,98; 5,75</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,1</t>
+          <t>0,25; 2,01</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 7,92</t>
+          <t>0,16; 7,65</t>
         </is>
       </c>
     </row>
@@ -861,22 +861,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 5,09</t>
+          <t>0,12; 5,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 8,48</t>
+          <t>0,1; 7,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,12</t>
+          <t>0,6; 4,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,2</t>
+          <t>0,0; 9,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -886,32 +886,32 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,16</t>
+          <t>0,36; 4,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 6,77</t>
+          <t>0,5; 6,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,43</t>
+          <t>0,0; 6,44</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,04; 2,71</t>
+          <t>0,06; 3,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 4,26</t>
+          <t>0,69; 4,08</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,87</t>
+          <t>1,01; 5,39</t>
         </is>
       </c>
     </row>
@@ -1001,27 +1001,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 10,66</t>
+          <t>1,16; 10,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,46</t>
+          <t>0,0; 11,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 7,53</t>
+          <t>0,7; 7,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 8,2</t>
+          <t>0,35; 7,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,15</t>
+          <t>0,0; 10,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1031,27 +1031,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 8,21</t>
+          <t>0,24; 8,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 6,02</t>
+          <t>0,43; 6,55</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 8,4</t>
+          <t>1,37; 8,62</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,75</t>
+          <t>0,0; 5,72</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 5,89</t>
+          <t>0,99; 5,96</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,46</t>
+          <t>0,0; 10,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1146,52 +1146,52 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,67</t>
+          <t>0,0; 0,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,75</t>
+          <t>0,0; 0,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,2</t>
+          <t>0,0; 5,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,59</t>
+          <t>0,0; 4,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,15</t>
+          <t>0,0; 9,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 9,95</t>
+          <t>0,17; 9,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 6,22</t>
+          <t>0,84; 5,99</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,41</t>
+          <t>0,0; 3,34</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,02</t>
+          <t>0,0; 4,69</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,12; 5,21</t>
+          <t>0,13; 5,44</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 7,22</t>
+          <t>1,65; 7,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,63</t>
+          <t>1,2; 4,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,96</t>
+          <t>0,53; 3,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,34</t>
+          <t>0,6; 3,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,66</t>
+          <t>1,66; 5,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,36</t>
+          <t>0,23; 2,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,95</t>
+          <t>0,42; 3,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 5,18</t>
+          <t>1,05; 5,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,97; 5,21</t>
+          <t>1,97; 5,13</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,98</t>
+          <t>0,91; 2,87</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,76</t>
+          <t>0,71; 2,67</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,9</t>
+          <t>1,18; 4,17</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ09_D-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_D-Edad-trans_orig.xlsx
@@ -716,17 +716,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 16,09</t>
+          <t>1,35; 16,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 8,93</t>
+          <t>1,3; 8,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 2,82</t>
+          <t>0,11; 2,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,7; 14,11</t>
+          <t>2,74; 14,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,82</t>
+          <t>0,0; 2,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,26</t>
+          <t>0,0; 2,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -756,17 +756,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,61; 13,17</t>
+          <t>3,94; 12,69</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 5,75</t>
+          <t>1,01; 6,11</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,01</t>
+          <t>0,23; 1,99</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -861,22 +861,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 5,86</t>
+          <t>0,13; 5,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 7,51</t>
+          <t>0,19; 8,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 4,08</t>
+          <t>0,7; 4,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,87</t>
+          <t>0,0; 8,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -886,32 +886,32 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 4,51</t>
+          <t>0,47; 4,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 6,88</t>
+          <t>0,58; 6,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,44</t>
+          <t>0,0; 5,39</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 3,06</t>
+          <t>0,06; 3,31</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,08</t>
+          <t>0,69; 4,24</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,39</t>
+          <t>1,05; 5,16</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 10,86</t>
+          <t>1,2; 11,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 7,45</t>
+          <t>0,71; 6,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 7,51</t>
+          <t>0,34; 7,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,17</t>
+          <t>0,0; 9,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1031,27 +1031,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 8,53</t>
+          <t>0,51; 9,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 6,55</t>
+          <t>0,43; 6,62</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 8,62</t>
+          <t>1,44; 8,69</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,72</t>
+          <t>0,0; 5,97</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 5,96</t>
+          <t>1,05; 6,41</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,83</t>
+          <t>0,0; 0,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1156,42 +1156,42 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,91</t>
+          <t>0,0; 5,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,46</t>
+          <t>0,0; 6,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,2</t>
+          <t>0,0; 9,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 9,46</t>
+          <t>0,17; 11,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,99</t>
+          <t>0,85; 5,89</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,34</t>
+          <t>0,0; 3,51</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,69</t>
+          <t>0,0; 5,25</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,13; 5,44</t>
+          <t>0,12; 5,85</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,65; 7,4</t>
+          <t>1,52; 7,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,67</t>
+          <t>1,15; 4,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,89</t>
+          <t>0,55; 3,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,41</t>
+          <t>0,53; 3,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,65</t>
+          <t>1,52; 5,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,51</t>
+          <t>0,3; 2,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,13</t>
+          <t>0,45; 3,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 5,35</t>
+          <t>1,18; 5,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,97; 5,13</t>
+          <t>2,02; 5,4</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,87</t>
+          <t>0,89; 2,94</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,67</t>
+          <t>0,69; 2,65</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,17</t>
+          <t>1,13; 3,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ09_D-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_D-Edad-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7,87</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,71</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,53</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8,0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>8,52</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4,32</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1,09</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,11</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,87</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,71</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,53</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,0</t>
+          <t>2,08</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,08</t>
+          <t>3,89</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 16,5</t>
+          <t>2,74; 14,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 8,92</t>
+          <t>0,0; 1,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 2,78</t>
+          <t>0,0; 2,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1,5; 16,5</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,31; 9,09</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0,11; 2,9</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>0,0; 7,5</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2,74; 14,88</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,02</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,28</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,94; 12,69</t>
+          <t>3,78; 12,83</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 6,11</t>
+          <t>0,96; 5,14</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,99</t>
+          <t>0,27; 2,1</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 7,65</t>
+          <t>0,22; 7,56</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2,18</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,57</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2,1</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1,29</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,5</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,26</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,18</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,57</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,17</t>
+          <t>2,13</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,2</t>
+          <t>2,11</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 10,2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,13; 5,55</t>
-        </is>
-      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 8,49</t>
+          <t>0,38; 4,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,16</t>
+          <t>0,49; 6,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,13; 5,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,35</t>
+          <t>0,19; 8,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 6,64</t>
+          <t>0,66; 3,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,39</t>
+          <t>0,0; 6,43</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 3,31</t>
+          <t>0,04; 2,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,24</t>
+          <t>0,79; 4,26</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 5,16</t>
+          <t>0,9; 4,56</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,41</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,93</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2,58</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>3,05</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4,76</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2,88</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,05</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,41</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,93</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,48</t>
+          <t>3,1</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,73</t>
+          <t>2,82</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0,34; 8,2</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 10,15</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0,31; 8,7</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>0,0; 12,15</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1,2; 11,26</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 11,67</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,71; 6,93</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,34; 7,26</t>
-        </is>
-      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,91</t>
+          <t>1,15; 10,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 11,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 9,07</t>
+          <t>0,65; 7,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 6,62</t>
+          <t>0,43; 6,02</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 8,69</t>
+          <t>1,18; 8,4</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,97</t>
+          <t>0,0; 5,75</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 6,41</t>
+          <t>0,86; 6,1</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2,01</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,11</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,95</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2,49</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>4,64</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0,19</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,01</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,11</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,95</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,43</t>
+          <t>0,24</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,34</t>
+          <t>1,78</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,72</t>
+          <t>0,0; 6,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>0,0; 4,59</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 9,15</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0,2; 10,27</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 9,46</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,78</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,81</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,57</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,13</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,15</t>
+          <t>0,0; 0,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 11,06</t>
+          <t>0,0; 1,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,89</t>
+          <t>0,99; 6,22</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,51</t>
+          <t>0,0; 3,41</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,25</t>
+          <t>0,0; 5,02</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,12; 5,85</t>
+          <t>0,2; 6,65</t>
         </is>
       </c>
     </row>
@@ -1208,54 +1208,54 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>3,25</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,91</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,24</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2,59</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>3,68</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2,58</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,64</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2,06</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>3,41</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>1,66</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,25</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,91</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,24</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>2,57</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>3,41</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>1,66</t>
-        </is>
-      </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
           <t>1,43</t>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,16</t>
+          <t>2,37</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 7,05</t>
+          <t>1,6; 5,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,83</t>
+          <t>0,24; 2,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,97</t>
+          <t>0,41; 2,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,55</t>
+          <t>0,96; 5,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 5,45</t>
+          <t>1,38; 7,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,38</t>
+          <t>1,15; 4,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,0</t>
+          <t>0,54; 3,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,35</t>
+          <t>0,93; 4,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,02; 5,4</t>
+          <t>1,97; 5,21</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,94</t>
+          <t>0,94; 2,98</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,65</t>
+          <t>0,73; 2,76</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,96</t>
+          <t>1,37; 4,45</t>
         </is>
       </c>
     </row>
